--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.0701586799882</v>
+        <v>2.611400785498082</v>
       </c>
       <c r="D2" t="n">
-        <v>8.970631093865251</v>
+        <v>1.457727552753103</v>
       </c>
       <c r="E2" t="n">
-        <v>8.690390548423212</v>
+        <v>1.412188464118772</v>
       </c>
       <c r="F2" t="n">
-        <v>10.71148706582328</v>
+        <v>1.740616648196283</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.998221151957975</v>
+        <v>1.299710937193171</v>
       </c>
       <c r="D3" t="n">
-        <v>8.762150709358339</v>
+        <v>1.42384949027073</v>
       </c>
       <c r="E3" t="n">
-        <v>8.690390548423212</v>
+        <v>1.412188464118772</v>
       </c>
       <c r="F3" t="n">
-        <v>10.71148706582328</v>
+        <v>1.740616648196283</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.29285557554183</v>
+        <v>4.922589031025547</v>
       </c>
       <c r="D4" t="n">
-        <v>17.76192036972884</v>
+        <v>2.886312060080937</v>
       </c>
       <c r="E4" t="n">
-        <v>8.690390548423212</v>
+        <v>1.412188464118772</v>
       </c>
       <c r="F4" t="n">
-        <v>10.71148706582328</v>
+        <v>1.740616648196283</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.00735135169495</v>
+        <v>2.763694594650429</v>
       </c>
       <c r="D5" t="n">
-        <v>9.003350834785463</v>
+        <v>1.463044510652638</v>
       </c>
       <c r="E5" t="n">
-        <v>8.690390548423212</v>
+        <v>1.412188464118772</v>
       </c>
       <c r="F5" t="n">
-        <v>10.71148706582328</v>
+        <v>1.740616648196283</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.410481645045</v>
+        <v>5.266703267319813</v>
       </c>
       <c r="D6" t="n">
-        <v>34.23037927650486</v>
+        <v>5.562436632432039</v>
       </c>
       <c r="E6" t="n">
-        <v>8.690390548423212</v>
+        <v>1.412188464118772</v>
       </c>
       <c r="F6" t="n">
-        <v>10.71148706582328</v>
+        <v>1.740616648196283</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.41695922883098</v>
+        <v>5.430255874685035</v>
       </c>
       <c r="D7" t="n">
-        <v>35.12871448232023</v>
+        <v>5.708416103377037</v>
       </c>
       <c r="E7" t="n">
-        <v>8.690390548423212</v>
+        <v>1.412188464118772</v>
       </c>
       <c r="F7" t="n">
-        <v>10.71148706582328</v>
+        <v>1.740616648196283</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.37759160320434</v>
+        <v>3.148858635520705</v>
       </c>
       <c r="D8" t="n">
-        <v>18.82294499945244</v>
+        <v>3.058728562411021</v>
       </c>
       <c r="E8" t="n">
-        <v>8.690390548423212</v>
+        <v>1.412188464118772</v>
       </c>
       <c r="F8" t="n">
-        <v>10.71148706582328</v>
+        <v>1.740616648196283</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6574597618142</v>
+        <v>4.656837211294808</v>
       </c>
       <c r="D9" t="n">
-        <v>30.61146803583</v>
+        <v>4.974363555822375</v>
       </c>
       <c r="E9" t="n">
-        <v>8.690390548423212</v>
+        <v>1.412188464118772</v>
       </c>
       <c r="F9" t="n">
-        <v>10.71148706582328</v>
+        <v>1.740616648196283</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
